--- a/TRPO_dolgs.xlsx
+++ b/TRPO_dolgs.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="14">
   <si>
     <t>№</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>Лабораторные работы (ТРПО)</t>
+  </si>
+  <si>
+    <t>мб 4 сделано</t>
+  </si>
+  <si>
+    <t>потенциально 5 заданий</t>
   </si>
 </sst>
 </file>
@@ -1268,13 +1274,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>4</v>
@@ -1283,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>4</v>
@@ -1305,16 +1311,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>4</v>
@@ -1335,7 +1341,9 @@
         <v>6</v>
       </c>
       <c r="L6" s="2"/>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1379,13 +1387,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>4</v>
@@ -1409,7 +1417,9 @@
         <v>6</v>
       </c>
       <c r="L8" s="2"/>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
